--- a/Intenções.xlsx
+++ b/Intenções.xlsx
@@ -420,10 +420,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A75"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="98" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -433,13 +435,21 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="n"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>HONRA E LOUVOR:</t>
+          <t>HONRA E LOUVOR</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>INTENÇÃO</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>7º DIA</t>
         </is>
       </c>
     </row>
@@ -449,6 +459,11 @@
           <t>Divino Espírito Santo</t>
         </is>
       </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Particular</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -456,6 +471,16 @@
           <t>Nossa Senhora Aparecida</t>
         </is>
       </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Vocações Sacerdotais</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>IRMÃOS FALECIDOS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -463,463 +488,460 @@
           <t>São José</t>
         </is>
       </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Conversão dos pecadores</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>+ Por todas as  Almas</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Beatificação Venerável Servo de Deus Padre Libério</t>
+          <t>Beatificação Venerável Se-</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Pelos colegas de Rogerio-</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>+ Raimunda Maria de Castr-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Nossa Senhora do Desterro</t>
+          <t>-rvo de Deus Padre Libério</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>-Pereira Castro da</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>-o e Jose de Castro, Terezinha Maria de Castro e Familiares falecidos</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>São Francisco de Paula</t>
+          <t>Nossa Senhora do Desterro</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>PRODEMGE Programa de Tecn-</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>+ Rogério Pereira Castro</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>São Sebastião</t>
+          <t>São Francisco de Paula</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>-ologia de Minas</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>+ Dorvalino Teodoro Perei-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Nossa Senhora do Desterro</t>
+          <t>São Sebastião</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>Marcelo Chula Bonfim</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>-ra e familiares falecidos</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Nossa senhora das Graças</t>
+          <t>Nossa Senhora do Desterro</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Rodrigo Braga  Chula</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>+Alaor Alves Vilano</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>São José</t>
+          <t>Nossa senhora das Graças</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Alfredo Dór da Silva e fa-</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>+Silvio Eustáquio da Silv-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Santo Onofre</t>
+          <t>São José</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>-mília</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>-a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Santa Edwiges</t>
+          <t>Santo Onofre</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>Daniel  Henrique  Silva</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>+Norvina Ana de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
+          <t>Santa Edwiges</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>Lucas  de Freitas Francel-</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>+Marcilio Soares Neto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
           <t>Santa Luzia</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>-ino</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>+ Miguel Vaz</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>INTENÇÃO:</t>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Lourival  de Freitas Mour-</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>+ Olimpia de Souza</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>ANIVERSÁRIO NATALÍCIO</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>-ão</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>+ Antônio Miguel Maia</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Vocações Sacerdotais</t>
+          <t>AMBROSIO BRASIL VELASCO</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>+ Altiva Gomes Brandão e-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Conversão dos pecadores</t>
+          <t>ANGELA MARIA TOMÉ</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO DE SAÚDE</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>-Domingos Brandão</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Pelos colegas de Rogerio Pereira Castro da</t>
+          <t>LUIZ CARLOS XAVIER</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>Todos os enfermos da Paró-</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>+ Maria de Carvalho Ribei-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>PRODEMGE Programa de Tecnologia de Minas</t>
+          <t>MARIA AUXILIADORA AMARAL-</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>-quia</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>-ro ( Dona Glorinha)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Marcelo Chula Bonfim</t>
+          <t>-NUNES</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>José Geraldo Rabelo Júnio-</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>+ Alaor Alves Vilano</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Rodrigo Braga  Chula</t>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>-r</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>+ Maria Policarpo Mourão</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Alfredo Dór da Silva e família</t>
+          <t>ANIVERSÁRIO DE CASAMENTO</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>Antônio Henrique de Castr-</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>+ Daniel José da Costa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Daniel  Henrique  Silva</t>
+          <t>VERA LUCIA BARBOSA LIMA-</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>-o e Geraldo Sinfrônico de Castro</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>+ Vicente Mereciano Gonça-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Lucas  de Freitas Francelino</t>
+          <t>-E  JOSE TARCISIO</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>-lves</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>Lourival  de Freitas Mourão</t>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>+ Adalgiza  Rita Gonçalve-</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n"/>
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>AÇÃO DE GRAÇAS</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>-s</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>ANIVERSÁRIO NATALÍCIO:</t>
+          <t>Família  Gontijo Silveira</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>+ José Amâncio Marques</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>AMBROSIO BRASIL VELASCO</t>
+          <t>Por uma graça alcançada</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>+ Bernardino Ivo</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>ANGELA MARIA TOMÉ</t>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>+Onofre  Evangelista Soar-</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>LUIZ CARLOS XAVIER</t>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>-es</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>MARIA AUXILIADORA AMARAL NUNES</t>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>+ Vicente Mereciano Gonça-</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n"/>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>-lves</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>RECUPERAÇÃO DE SAÚDE:</t>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>+ Adalgiza Rita Gonçalves</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Todos os enfermos da Paróquia</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>José Geraldo Rabelo Júnior</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Antônio Henrique de Castro e Geraldo Sinfrônico de Castro</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>ANIVERSÁRIO DE CASAMENTO:</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>VERA LUCIA BARBOSA LIMA  E  JOSE TARCISIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>AÇÃO DE GRAÇAS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>Família  Gontijo Silveira</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>Por uma graça alcançada</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>IRMÃOS FALECIDOS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>+ Por todas as  Almas</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>+ Raimunda Maria de Castro e Jose de Castro, Terezinha Maria de Castro e Familiares falecidos</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>+ Rogério Pereira Castro</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>+ Dorvalino Teodoro Pereira e familiares falecidos</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>+Alaor Alves Vilano</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>+Silvio Eustáquio da Silva</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>+Norvina Ana de Oliveira</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>+Marcilio Soares Neto</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>+ Miguel Vaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>+ Olimpia de Souza</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>+ Antônio Miguel Maia</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>+ Altiva Gomes Brandão e Domingos Brandão</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>+ Maria de Carvalho Ribeiro ( Dona Glorinha)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>+ Alaor Alves Vilano</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>+ Maria Policarpo Mourão</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>+ Daniel José da Costa</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>+ Vicente Mereciano Gonçalves</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr">
-        <is>
-          <t>+ Adalgiza  Rita Gonçalves</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>+ José Amâncio Marques</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr">
-        <is>
-          <t>+ Bernardino Ivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="inlineStr">
-        <is>
-          <t>+Onofre  Evangelista Soares</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="inlineStr">
-        <is>
-          <t>+ Vicente Mereciano Gonçalves</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="inlineStr">
-        <is>
-          <t>+ Adalgiza Rita Gonçalves</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr">
-        <is>
-          <t>+ José Amâncio Marques</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr">
-        <is>
-          <t>7º DIA:</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>